--- a/RESULTS/hydronewsfr/hydronewsfr_results.xlsx
+++ b/RESULTS/hydronewsfr/hydronewsfr_results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evangeliazve/Documents/Papier EMNLP/Dossier Github - supp material/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401A9AE4-D9F8-BC4A-9748-7D23BA9C4677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DD1DE6A-BCA4-3640-AC49-B2BA83CC26FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="800" windowWidth="29400" windowHeight="17000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="ml_metrics_with_ablation" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ml_metrics_with_ablation!$A$1:$T$325</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ml_metrics_with_ablation!$A$1:$T$289</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="35">
   <si>
     <t>horizon</t>
   </si>
@@ -517,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:T325"/>
+  <dimension ref="A1:T289"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
@@ -18459,2240 +18459,8 @@
         <v>0.26687916703241998</v>
       </c>
     </row>
-    <row r="290" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A290" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B290" s="2">
-        <v>9</v>
-      </c>
-      <c r="C290" s="2">
-        <v>9</v>
-      </c>
-      <c r="D290" s="2">
-        <v>0</v>
-      </c>
-      <c r="E290" s="2">
-        <v>5</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G290" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H290" s="2">
-        <v>17</v>
-      </c>
-      <c r="I290" s="2">
-        <v>3</v>
-      </c>
-      <c r="J290" s="2">
-        <v>14</v>
-      </c>
-      <c r="K290" s="2">
-        <v>0.46666666666666662</v>
-      </c>
-      <c r="L290" s="2">
-        <v>4.7140452079103161E-2</v>
-      </c>
-      <c r="M290" s="2">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="N290" s="2">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="O290" s="2">
-        <v>1</v>
-      </c>
-      <c r="P290" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q290" s="2">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="R290" s="2">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="S290" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T290" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A291" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B291" s="2">
-        <v>9</v>
-      </c>
-      <c r="C291" s="2">
-        <v>9</v>
-      </c>
-      <c r="D291" s="2">
-        <v>0</v>
-      </c>
-      <c r="E291" s="2">
-        <v>5</v>
-      </c>
-      <c r="F291" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G291" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H291" s="2">
-        <v>17</v>
-      </c>
-      <c r="I291" s="2">
-        <v>3</v>
-      </c>
-      <c r="J291" s="2">
-        <v>14</v>
-      </c>
-      <c r="K291" s="2">
-        <v>0</v>
-      </c>
-      <c r="L291" s="2">
-        <v>0</v>
-      </c>
-      <c r="M291" s="2">
-        <v>0</v>
-      </c>
-      <c r="N291" s="2">
-        <v>0</v>
-      </c>
-      <c r="O291" s="2">
-        <v>0</v>
-      </c>
-      <c r="P291" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q291" s="2">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="R291" s="2">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="S291" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T291" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A292" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B292" s="2">
-        <v>9</v>
-      </c>
-      <c r="C292" s="2">
-        <v>9</v>
-      </c>
-      <c r="D292" s="2">
-        <v>0</v>
-      </c>
-      <c r="E292" s="2">
-        <v>5</v>
-      </c>
-      <c r="F292" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G292" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H292" s="2">
-        <v>17</v>
-      </c>
-      <c r="I292" s="2">
-        <v>3</v>
-      </c>
-      <c r="J292" s="2">
-        <v>14</v>
-      </c>
-      <c r="K292" s="2">
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="L292" s="2">
-        <v>0.15713484026367719</v>
-      </c>
-      <c r="M292" s="2">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N292" s="2">
-        <v>0.23570226039551581</v>
-      </c>
-      <c r="O292" s="2">
-        <v>1</v>
-      </c>
-      <c r="P292" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q292" s="2">
-        <v>1</v>
-      </c>
-      <c r="R292" s="2">
-        <v>0</v>
-      </c>
-      <c r="S292" s="2">
-        <v>1</v>
-      </c>
-      <c r="T292" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A293" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B293" s="2">
-        <v>9</v>
-      </c>
-      <c r="C293" s="2">
-        <v>9</v>
-      </c>
-      <c r="D293" s="2">
-        <v>0</v>
-      </c>
-      <c r="E293" s="2">
-        <v>5</v>
-      </c>
-      <c r="F293" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G293" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H293" s="2">
-        <v>17</v>
-      </c>
-      <c r="I293" s="2">
-        <v>3</v>
-      </c>
-      <c r="J293" s="2">
-        <v>14</v>
-      </c>
-      <c r="K293" s="2">
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="L293" s="2">
-        <v>0.15713484026367719</v>
-      </c>
-      <c r="M293" s="2">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N293" s="2">
-        <v>0.23570226039551581</v>
-      </c>
-      <c r="O293" s="2">
-        <v>1</v>
-      </c>
-      <c r="P293" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q293" s="2">
-        <v>1</v>
-      </c>
-      <c r="R293" s="2">
-        <v>0</v>
-      </c>
-      <c r="S293" s="2">
-        <v>1</v>
-      </c>
-      <c r="T293" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A294" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B294" s="2">
-        <v>9</v>
-      </c>
-      <c r="C294" s="2">
-        <v>9</v>
-      </c>
-      <c r="D294" s="2">
-        <v>0</v>
-      </c>
-      <c r="E294" s="2">
-        <v>5</v>
-      </c>
-      <c r="F294" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G294" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H294" s="2">
-        <v>17</v>
-      </c>
-      <c r="I294" s="2">
-        <v>3</v>
-      </c>
-      <c r="J294" s="2">
-        <v>14</v>
-      </c>
-      <c r="K294" s="2">
-        <v>0</v>
-      </c>
-      <c r="L294" s="2">
-        <v>0</v>
-      </c>
-      <c r="M294" s="2">
-        <v>0</v>
-      </c>
-      <c r="N294" s="2">
-        <v>0</v>
-      </c>
-      <c r="O294" s="2">
-        <v>0</v>
-      </c>
-      <c r="P294" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q294" s="2">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="R294" s="2">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="S294" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T294" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A295" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B295" s="2">
-        <v>9</v>
-      </c>
-      <c r="C295" s="2">
-        <v>9</v>
-      </c>
-      <c r="D295" s="2">
-        <v>0</v>
-      </c>
-      <c r="E295" s="2">
-        <v>5</v>
-      </c>
-      <c r="F295" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G295" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H295" s="2">
-        <v>17</v>
-      </c>
-      <c r="I295" s="2">
-        <v>3</v>
-      </c>
-      <c r="J295" s="2">
-        <v>14</v>
-      </c>
-      <c r="K295" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="L295" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="M295" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N295" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="O295" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="P295" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="Q295" s="2">
-        <v>1</v>
-      </c>
-      <c r="R295" s="2">
-        <v>0</v>
-      </c>
-      <c r="S295" s="2">
-        <v>1</v>
-      </c>
-      <c r="T295" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A296" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B296" s="2">
-        <v>9</v>
-      </c>
-      <c r="C296" s="2">
-        <v>9</v>
-      </c>
-      <c r="D296" s="2">
-        <v>0</v>
-      </c>
-      <c r="E296" s="2">
-        <v>5</v>
-      </c>
-      <c r="F296" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G296" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H296" s="2">
-        <v>17</v>
-      </c>
-      <c r="I296" s="2">
-        <v>3</v>
-      </c>
-      <c r="J296" s="2">
-        <v>14</v>
-      </c>
-      <c r="K296" s="2">
-        <v>0</v>
-      </c>
-      <c r="L296" s="2">
-        <v>0</v>
-      </c>
-      <c r="M296" s="2">
-        <v>0</v>
-      </c>
-      <c r="N296" s="2">
-        <v>0</v>
-      </c>
-      <c r="O296" s="2">
-        <v>0</v>
-      </c>
-      <c r="P296" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q296" s="2">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="R296" s="2">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="S296" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T296" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A297" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B297" s="2">
-        <v>9</v>
-      </c>
-      <c r="C297" s="2">
-        <v>9</v>
-      </c>
-      <c r="D297" s="2">
-        <v>0</v>
-      </c>
-      <c r="E297" s="2">
-        <v>5</v>
-      </c>
-      <c r="F297" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G297" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H297" s="2">
-        <v>17</v>
-      </c>
-      <c r="I297" s="2">
-        <v>3</v>
-      </c>
-      <c r="J297" s="2">
-        <v>14</v>
-      </c>
-      <c r="K297" s="2">
-        <v>0.77777777777777768</v>
-      </c>
-      <c r="L297" s="2">
-        <v>0.15713484026367719</v>
-      </c>
-      <c r="M297" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N297" s="2">
-        <v>0.23570226039551581</v>
-      </c>
-      <c r="O297" s="2">
-        <v>1</v>
-      </c>
-      <c r="P297" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q297" s="2">
-        <v>1</v>
-      </c>
-      <c r="R297" s="2">
-        <v>0</v>
-      </c>
-      <c r="S297" s="2">
-        <v>1</v>
-      </c>
-      <c r="T297" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A298" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B298" s="2">
-        <v>9</v>
-      </c>
-      <c r="C298" s="2">
-        <v>9</v>
-      </c>
-      <c r="D298" s="2">
-        <v>0</v>
-      </c>
-      <c r="E298" s="2">
-        <v>5</v>
-      </c>
-      <c r="F298" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G298" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H298" s="2">
-        <v>17</v>
-      </c>
-      <c r="I298" s="2">
-        <v>3</v>
-      </c>
-      <c r="J298" s="2">
-        <v>14</v>
-      </c>
-      <c r="K298" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="L298" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="M298" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N298" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="O298" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="P298" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="Q298" s="2">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="R298" s="2">
-        <v>0.23570226039551581</v>
-      </c>
-      <c r="S298" s="2">
-        <v>0.88888888888888895</v>
-      </c>
-      <c r="T298" s="2">
-        <v>0.15713484026367719</v>
-      </c>
-    </row>
-    <row r="299" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A299" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B299" s="2">
-        <v>9</v>
-      </c>
-      <c r="C299" s="2">
-        <v>9</v>
-      </c>
-      <c r="D299" s="2">
-        <v>0</v>
-      </c>
-      <c r="E299" s="2">
-        <v>5</v>
-      </c>
-      <c r="F299" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G299" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H299" s="2">
-        <v>17</v>
-      </c>
-      <c r="I299" s="2">
-        <v>3</v>
-      </c>
-      <c r="J299" s="2">
-        <v>14</v>
-      </c>
-      <c r="K299" s="2">
-        <v>0</v>
-      </c>
-      <c r="L299" s="2">
-        <v>0</v>
-      </c>
-      <c r="M299" s="2">
-        <v>0</v>
-      </c>
-      <c r="N299" s="2">
-        <v>0</v>
-      </c>
-      <c r="O299" s="2">
-        <v>0</v>
-      </c>
-      <c r="P299" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q299" s="2">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="R299" s="2">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="S299" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T299" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A300" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B300" s="2">
-        <v>9</v>
-      </c>
-      <c r="C300" s="2">
-        <v>9</v>
-      </c>
-      <c r="D300" s="2">
-        <v>0</v>
-      </c>
-      <c r="E300" s="2">
-        <v>5</v>
-      </c>
-      <c r="F300" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G300" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H300" s="2">
-        <v>17</v>
-      </c>
-      <c r="I300" s="2">
-        <v>3</v>
-      </c>
-      <c r="J300" s="2">
-        <v>14</v>
-      </c>
-      <c r="K300" s="2">
-        <v>0</v>
-      </c>
-      <c r="L300" s="2">
-        <v>0</v>
-      </c>
-      <c r="M300" s="2">
-        <v>0</v>
-      </c>
-      <c r="N300" s="2">
-        <v>0</v>
-      </c>
-      <c r="O300" s="2">
-        <v>0</v>
-      </c>
-      <c r="P300" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q300" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="R300" s="2">
-        <v>0.23570226039551581</v>
-      </c>
-      <c r="S300" s="2">
-        <v>0.72222222222222232</v>
-      </c>
-      <c r="T300" s="2">
-        <v>0.2078698548207745</v>
-      </c>
-    </row>
-    <row r="301" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A301" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B301" s="2">
-        <v>9</v>
-      </c>
-      <c r="C301" s="2">
-        <v>9</v>
-      </c>
-      <c r="D301" s="2">
-        <v>0</v>
-      </c>
-      <c r="E301" s="2">
-        <v>5</v>
-      </c>
-      <c r="F301" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G301" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H301" s="2">
-        <v>17</v>
-      </c>
-      <c r="I301" s="2">
-        <v>3</v>
-      </c>
-      <c r="J301" s="2">
-        <v>14</v>
-      </c>
-      <c r="K301" s="2">
-        <v>0</v>
-      </c>
-      <c r="L301" s="2">
-        <v>0</v>
-      </c>
-      <c r="M301" s="2">
-        <v>0</v>
-      </c>
-      <c r="N301" s="2">
-        <v>0</v>
-      </c>
-      <c r="O301" s="2">
-        <v>0</v>
-      </c>
-      <c r="P301" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q301" s="2">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="R301" s="2">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="S301" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T301" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A302" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B302" s="2">
-        <v>9</v>
-      </c>
-      <c r="C302" s="2">
-        <v>9</v>
-      </c>
-      <c r="D302" s="2">
-        <v>0</v>
-      </c>
-      <c r="E302" s="2">
-        <v>5</v>
-      </c>
-      <c r="F302" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G302" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H302" s="2">
-        <v>17</v>
-      </c>
-      <c r="I302" s="2">
-        <v>3</v>
-      </c>
-      <c r="J302" s="2">
-        <v>14</v>
-      </c>
-      <c r="K302" s="2">
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="L302" s="2">
-        <v>0.15713484026367719</v>
-      </c>
-      <c r="M302" s="2">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N302" s="2">
-        <v>0.23570226039551581</v>
-      </c>
-      <c r="O302" s="2">
-        <v>1</v>
-      </c>
-      <c r="P302" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q302" s="2">
-        <v>1</v>
-      </c>
-      <c r="R302" s="2">
-        <v>0</v>
-      </c>
-      <c r="S302" s="2">
-        <v>1</v>
-      </c>
-      <c r="T302" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A303" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B303" s="2">
-        <v>9</v>
-      </c>
-      <c r="C303" s="2">
-        <v>9</v>
-      </c>
-      <c r="D303" s="2">
-        <v>0</v>
-      </c>
-      <c r="E303" s="2">
-        <v>5</v>
-      </c>
-      <c r="F303" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G303" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H303" s="2">
-        <v>17</v>
-      </c>
-      <c r="I303" s="2">
-        <v>3</v>
-      </c>
-      <c r="J303" s="2">
-        <v>14</v>
-      </c>
-      <c r="K303" s="2">
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="L303" s="2">
-        <v>0.15713484026367719</v>
-      </c>
-      <c r="M303" s="2">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N303" s="2">
-        <v>0.23570226039551581</v>
-      </c>
-      <c r="O303" s="2">
-        <v>1</v>
-      </c>
-      <c r="P303" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q303" s="2">
-        <v>1</v>
-      </c>
-      <c r="R303" s="2">
-        <v>0</v>
-      </c>
-      <c r="S303" s="2">
-        <v>1</v>
-      </c>
-      <c r="T303" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A304" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B304" s="2">
-        <v>9</v>
-      </c>
-      <c r="C304" s="2">
-        <v>9</v>
-      </c>
-      <c r="D304" s="2">
-        <v>0</v>
-      </c>
-      <c r="E304" s="2">
-        <v>5</v>
-      </c>
-      <c r="F304" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G304" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H304" s="2">
-        <v>17</v>
-      </c>
-      <c r="I304" s="2">
-        <v>3</v>
-      </c>
-      <c r="J304" s="2">
-        <v>14</v>
-      </c>
-      <c r="K304" s="2">
-        <v>0</v>
-      </c>
-      <c r="L304" s="2">
-        <v>0</v>
-      </c>
-      <c r="M304" s="2">
-        <v>0</v>
-      </c>
-      <c r="N304" s="2">
-        <v>0</v>
-      </c>
-      <c r="O304" s="2">
-        <v>0</v>
-      </c>
-      <c r="P304" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q304" s="2">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="R304" s="2">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="S304" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T304" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A305" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B305" s="2">
-        <v>9</v>
-      </c>
-      <c r="C305" s="2">
-        <v>9</v>
-      </c>
-      <c r="D305" s="2">
-        <v>0</v>
-      </c>
-      <c r="E305" s="2">
-        <v>5</v>
-      </c>
-      <c r="F305" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G305" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H305" s="2">
-        <v>17</v>
-      </c>
-      <c r="I305" s="2">
-        <v>3</v>
-      </c>
-      <c r="J305" s="2">
-        <v>14</v>
-      </c>
-      <c r="K305" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="L305" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="M305" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N305" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="O305" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="P305" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="Q305" s="2">
-        <v>1</v>
-      </c>
-      <c r="R305" s="2">
-        <v>0</v>
-      </c>
-      <c r="S305" s="2">
-        <v>1</v>
-      </c>
-      <c r="T305" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A306" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B306" s="2">
-        <v>9</v>
-      </c>
-      <c r="C306" s="2">
-        <v>9</v>
-      </c>
-      <c r="D306" s="2">
-        <v>0</v>
-      </c>
-      <c r="E306" s="2">
-        <v>5</v>
-      </c>
-      <c r="F306" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G306" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H306" s="2">
-        <v>17</v>
-      </c>
-      <c r="I306" s="2">
-        <v>3</v>
-      </c>
-      <c r="J306" s="2">
-        <v>14</v>
-      </c>
-      <c r="K306" s="2">
-        <v>0</v>
-      </c>
-      <c r="L306" s="2">
-        <v>0</v>
-      </c>
-      <c r="M306" s="2">
-        <v>0</v>
-      </c>
-      <c r="N306" s="2">
-        <v>0</v>
-      </c>
-      <c r="O306" s="2">
-        <v>0</v>
-      </c>
-      <c r="P306" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q306" s="2">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="R306" s="2">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="S306" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T306" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A307" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B307" s="2">
-        <v>9</v>
-      </c>
-      <c r="C307" s="2">
-        <v>9</v>
-      </c>
-      <c r="D307" s="2">
-        <v>0</v>
-      </c>
-      <c r="E307" s="2">
-        <v>5</v>
-      </c>
-      <c r="F307" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G307" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H307" s="2">
-        <v>17</v>
-      </c>
-      <c r="I307" s="2">
-        <v>3</v>
-      </c>
-      <c r="J307" s="2">
-        <v>14</v>
-      </c>
-      <c r="K307" s="2">
-        <v>1</v>
-      </c>
-      <c r="L307" s="2">
-        <v>0</v>
-      </c>
-      <c r="M307" s="2">
-        <v>1</v>
-      </c>
-      <c r="N307" s="2">
-        <v>0</v>
-      </c>
-      <c r="O307" s="2">
-        <v>1</v>
-      </c>
-      <c r="P307" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q307" s="2">
-        <v>1</v>
-      </c>
-      <c r="R307" s="2">
-        <v>0</v>
-      </c>
-      <c r="S307" s="2">
-        <v>1</v>
-      </c>
-      <c r="T307" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A308" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B308" s="2">
-        <v>9</v>
-      </c>
-      <c r="C308" s="2">
-        <v>9</v>
-      </c>
-      <c r="D308" s="2">
-        <v>0</v>
-      </c>
-      <c r="E308" s="2">
-        <v>5</v>
-      </c>
-      <c r="F308" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G308" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H308" s="2">
-        <v>17</v>
-      </c>
-      <c r="I308" s="2">
-        <v>3</v>
-      </c>
-      <c r="J308" s="2">
-        <v>14</v>
-      </c>
-      <c r="K308" s="2">
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="L308" s="2">
-        <v>0.15713484026367719</v>
-      </c>
-      <c r="M308" s="2">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N308" s="2">
-        <v>0.23570226039551581</v>
-      </c>
-      <c r="O308" s="2">
-        <v>1</v>
-      </c>
-      <c r="P308" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q308" s="2">
-        <v>1</v>
-      </c>
-      <c r="R308" s="2">
-        <v>0</v>
-      </c>
-      <c r="S308" s="2">
-        <v>1</v>
-      </c>
-      <c r="T308" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A309" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B309" s="2">
-        <v>9</v>
-      </c>
-      <c r="C309" s="2">
-        <v>9</v>
-      </c>
-      <c r="D309" s="2">
-        <v>0</v>
-      </c>
-      <c r="E309" s="2">
-        <v>5</v>
-      </c>
-      <c r="F309" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G309" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H309" s="2">
-        <v>17</v>
-      </c>
-      <c r="I309" s="2">
-        <v>3</v>
-      </c>
-      <c r="J309" s="2">
-        <v>14</v>
-      </c>
-      <c r="K309" s="2">
-        <v>0</v>
-      </c>
-      <c r="L309" s="2">
-        <v>0</v>
-      </c>
-      <c r="M309" s="2">
-        <v>0</v>
-      </c>
-      <c r="N309" s="2">
-        <v>0</v>
-      </c>
-      <c r="O309" s="2">
-        <v>0</v>
-      </c>
-      <c r="P309" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q309" s="2">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="R309" s="2">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="S309" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T309" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A310" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B310" s="2">
-        <v>9</v>
-      </c>
-      <c r="C310" s="2">
-        <v>9</v>
-      </c>
-      <c r="D310" s="2">
-        <v>0</v>
-      </c>
-      <c r="E310" s="2">
-        <v>5</v>
-      </c>
-      <c r="F310" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G310" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H310" s="2">
-        <v>17</v>
-      </c>
-      <c r="I310" s="2">
-        <v>3</v>
-      </c>
-      <c r="J310" s="2">
-        <v>14</v>
-      </c>
-      <c r="K310" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="L310" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="M310" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N310" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="O310" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="P310" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="Q310" s="2">
-        <v>1</v>
-      </c>
-      <c r="R310" s="2">
-        <v>0</v>
-      </c>
-      <c r="S310" s="2">
-        <v>1</v>
-      </c>
-      <c r="T310" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A311" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B311" s="2">
-        <v>9</v>
-      </c>
-      <c r="C311" s="2">
-        <v>9</v>
-      </c>
-      <c r="D311" s="2">
-        <v>0</v>
-      </c>
-      <c r="E311" s="2">
-        <v>5</v>
-      </c>
-      <c r="F311" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G311" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H311" s="2">
-        <v>17</v>
-      </c>
-      <c r="I311" s="2">
-        <v>3</v>
-      </c>
-      <c r="J311" s="2">
-        <v>14</v>
-      </c>
-      <c r="K311" s="2">
-        <v>0</v>
-      </c>
-      <c r="L311" s="2">
-        <v>0</v>
-      </c>
-      <c r="M311" s="2">
-        <v>0</v>
-      </c>
-      <c r="N311" s="2">
-        <v>0</v>
-      </c>
-      <c r="O311" s="2">
-        <v>0</v>
-      </c>
-      <c r="P311" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q311" s="2">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="R311" s="2">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="S311" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T311" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A312" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B312" s="2">
-        <v>9</v>
-      </c>
-      <c r="C312" s="2">
-        <v>9</v>
-      </c>
-      <c r="D312" s="2">
-        <v>0</v>
-      </c>
-      <c r="E312" s="2">
-        <v>5</v>
-      </c>
-      <c r="F312" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G312" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H312" s="2">
-        <v>17</v>
-      </c>
-      <c r="I312" s="2">
-        <v>3</v>
-      </c>
-      <c r="J312" s="2">
-        <v>14</v>
-      </c>
-      <c r="K312" s="2">
-        <v>1</v>
-      </c>
-      <c r="L312" s="2">
-        <v>0</v>
-      </c>
-      <c r="M312" s="2">
-        <v>1</v>
-      </c>
-      <c r="N312" s="2">
-        <v>0</v>
-      </c>
-      <c r="O312" s="2">
-        <v>1</v>
-      </c>
-      <c r="P312" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q312" s="2">
-        <v>1</v>
-      </c>
-      <c r="R312" s="2">
-        <v>0</v>
-      </c>
-      <c r="S312" s="2">
-        <v>1</v>
-      </c>
-      <c r="T312" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A313" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B313" s="2">
-        <v>9</v>
-      </c>
-      <c r="C313" s="2">
-        <v>9</v>
-      </c>
-      <c r="D313" s="2">
-        <v>0</v>
-      </c>
-      <c r="E313" s="2">
-        <v>5</v>
-      </c>
-      <c r="F313" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G313" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H313" s="2">
-        <v>17</v>
-      </c>
-      <c r="I313" s="2">
-        <v>3</v>
-      </c>
-      <c r="J313" s="2">
-        <v>14</v>
-      </c>
-      <c r="K313" s="2">
-        <v>1</v>
-      </c>
-      <c r="L313" s="2">
-        <v>0</v>
-      </c>
-      <c r="M313" s="2">
-        <v>1</v>
-      </c>
-      <c r="N313" s="2">
-        <v>0</v>
-      </c>
-      <c r="O313" s="2">
-        <v>1</v>
-      </c>
-      <c r="P313" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q313" s="2">
-        <v>1</v>
-      </c>
-      <c r="R313" s="2">
-        <v>0</v>
-      </c>
-      <c r="S313" s="2">
-        <v>1</v>
-      </c>
-      <c r="T313" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A314" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B314" s="2">
-        <v>9</v>
-      </c>
-      <c r="C314" s="2">
-        <v>9</v>
-      </c>
-      <c r="D314" s="2">
-        <v>0</v>
-      </c>
-      <c r="E314" s="2">
-        <v>5</v>
-      </c>
-      <c r="F314" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G314" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H314" s="2">
-        <v>17</v>
-      </c>
-      <c r="I314" s="2">
-        <v>3</v>
-      </c>
-      <c r="J314" s="2">
-        <v>14</v>
-      </c>
-      <c r="K314" s="2">
-        <v>0</v>
-      </c>
-      <c r="L314" s="2">
-        <v>0</v>
-      </c>
-      <c r="M314" s="2">
-        <v>0</v>
-      </c>
-      <c r="N314" s="2">
-        <v>0</v>
-      </c>
-      <c r="O314" s="2">
-        <v>0</v>
-      </c>
-      <c r="P314" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q314" s="2">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="R314" s="2">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="S314" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T314" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A315" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B315" s="2">
-        <v>9</v>
-      </c>
-      <c r="C315" s="2">
-        <v>9</v>
-      </c>
-      <c r="D315" s="2">
-        <v>0</v>
-      </c>
-      <c r="E315" s="2">
-        <v>5</v>
-      </c>
-      <c r="F315" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G315" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H315" s="2">
-        <v>17</v>
-      </c>
-      <c r="I315" s="2">
-        <v>3</v>
-      </c>
-      <c r="J315" s="2">
-        <v>14</v>
-      </c>
-      <c r="K315" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="L315" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="M315" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N315" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="O315" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="P315" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="Q315" s="2">
-        <v>1</v>
-      </c>
-      <c r="R315" s="2">
-        <v>0</v>
-      </c>
-      <c r="S315" s="2">
-        <v>1</v>
-      </c>
-      <c r="T315" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A316" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B316" s="2">
-        <v>9</v>
-      </c>
-      <c r="C316" s="2">
-        <v>9</v>
-      </c>
-      <c r="D316" s="2">
-        <v>0</v>
-      </c>
-      <c r="E316" s="2">
-        <v>5</v>
-      </c>
-      <c r="F316" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G316" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H316" s="2">
-        <v>17</v>
-      </c>
-      <c r="I316" s="2">
-        <v>3</v>
-      </c>
-      <c r="J316" s="2">
-        <v>14</v>
-      </c>
-      <c r="K316" s="2">
-        <v>0</v>
-      </c>
-      <c r="L316" s="2">
-        <v>0</v>
-      </c>
-      <c r="M316" s="2">
-        <v>0</v>
-      </c>
-      <c r="N316" s="2">
-        <v>0</v>
-      </c>
-      <c r="O316" s="2">
-        <v>0</v>
-      </c>
-      <c r="P316" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q316" s="2">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="R316" s="2">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="S316" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T316" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A317" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B317" s="2">
-        <v>9</v>
-      </c>
-      <c r="C317" s="2">
-        <v>9</v>
-      </c>
-      <c r="D317" s="2">
-        <v>0</v>
-      </c>
-      <c r="E317" s="2">
-        <v>5</v>
-      </c>
-      <c r="F317" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G317" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H317" s="2">
-        <v>17</v>
-      </c>
-      <c r="I317" s="2">
-        <v>3</v>
-      </c>
-      <c r="J317" s="2">
-        <v>14</v>
-      </c>
-      <c r="K317" s="2">
-        <v>0.61111111111111105</v>
-      </c>
-      <c r="L317" s="2">
-        <v>7.8567420131838595E-2</v>
-      </c>
-      <c r="M317" s="2">
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="N317" s="2">
-        <v>7.8567420131838622E-2</v>
-      </c>
-      <c r="O317" s="2">
-        <v>1</v>
-      </c>
-      <c r="P317" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q317" s="2">
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="R317" s="2">
-        <v>7.8567420131838622E-2</v>
-      </c>
-      <c r="S317" s="2">
-        <v>0.72222222222222232</v>
-      </c>
-      <c r="T317" s="2">
-        <v>3.928371006591927E-2</v>
-      </c>
-    </row>
-    <row r="318" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A318" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B318" s="2">
-        <v>9</v>
-      </c>
-      <c r="C318" s="2">
-        <v>9</v>
-      </c>
-      <c r="D318" s="2">
-        <v>0</v>
-      </c>
-      <c r="E318" s="2">
-        <v>5</v>
-      </c>
-      <c r="F318" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G318" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H318" s="2">
-        <v>17</v>
-      </c>
-      <c r="I318" s="2">
-        <v>3</v>
-      </c>
-      <c r="J318" s="2">
-        <v>14</v>
-      </c>
-      <c r="K318" s="2">
-        <v>0.61111111111111105</v>
-      </c>
-      <c r="L318" s="2">
-        <v>7.8567420131838595E-2</v>
-      </c>
-      <c r="M318" s="2">
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="N318" s="2">
-        <v>7.8567420131838622E-2</v>
-      </c>
-      <c r="O318" s="2">
-        <v>1</v>
-      </c>
-      <c r="P318" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q318" s="2">
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="R318" s="2">
-        <v>7.8567420131838622E-2</v>
-      </c>
-      <c r="S318" s="2">
-        <v>0.72222222222222232</v>
-      </c>
-      <c r="T318" s="2">
-        <v>3.928371006591927E-2</v>
-      </c>
-    </row>
-    <row r="319" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A319" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B319" s="2">
-        <v>9</v>
-      </c>
-      <c r="C319" s="2">
-        <v>9</v>
-      </c>
-      <c r="D319" s="2">
-        <v>0</v>
-      </c>
-      <c r="E319" s="2">
-        <v>5</v>
-      </c>
-      <c r="F319" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G319" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H319" s="2">
-        <v>17</v>
-      </c>
-      <c r="I319" s="2">
-        <v>3</v>
-      </c>
-      <c r="J319" s="2">
-        <v>14</v>
-      </c>
-      <c r="K319" s="2">
-        <v>0</v>
-      </c>
-      <c r="L319" s="2">
-        <v>0</v>
-      </c>
-      <c r="M319" s="2">
-        <v>0</v>
-      </c>
-      <c r="N319" s="2">
-        <v>0</v>
-      </c>
-      <c r="O319" s="2">
-        <v>0</v>
-      </c>
-      <c r="P319" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q319" s="2">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="R319" s="2">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="S319" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T319" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A320" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B320" s="2">
-        <v>9</v>
-      </c>
-      <c r="C320" s="2">
-        <v>9</v>
-      </c>
-      <c r="D320" s="2">
-        <v>0</v>
-      </c>
-      <c r="E320" s="2">
-        <v>5</v>
-      </c>
-      <c r="F320" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G320" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H320" s="2">
-        <v>17</v>
-      </c>
-      <c r="I320" s="2">
-        <v>3</v>
-      </c>
-      <c r="J320" s="2">
-        <v>14</v>
-      </c>
-      <c r="K320" s="2">
-        <v>0</v>
-      </c>
-      <c r="L320" s="2">
-        <v>0</v>
-      </c>
-      <c r="M320" s="2">
-        <v>0</v>
-      </c>
-      <c r="N320" s="2">
-        <v>0</v>
-      </c>
-      <c r="O320" s="2">
-        <v>0</v>
-      </c>
-      <c r="P320" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q320" s="2">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="R320" s="2">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="S320" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T320" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A321" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B321" s="2">
-        <v>9</v>
-      </c>
-      <c r="C321" s="2">
-        <v>9</v>
-      </c>
-      <c r="D321" s="2">
-        <v>0</v>
-      </c>
-      <c r="E321" s="2">
-        <v>5</v>
-      </c>
-      <c r="F321" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G321" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H321" s="2">
-        <v>17</v>
-      </c>
-      <c r="I321" s="2">
-        <v>3</v>
-      </c>
-      <c r="J321" s="2">
-        <v>14</v>
-      </c>
-      <c r="K321" s="2">
-        <v>0</v>
-      </c>
-      <c r="L321" s="2">
-        <v>0</v>
-      </c>
-      <c r="M321" s="2">
-        <v>0</v>
-      </c>
-      <c r="N321" s="2">
-        <v>0</v>
-      </c>
-      <c r="O321" s="2">
-        <v>0</v>
-      </c>
-      <c r="P321" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q321" s="2">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="R321" s="2">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="S321" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T321" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A322" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B322" s="2">
-        <v>9</v>
-      </c>
-      <c r="C322" s="2">
-        <v>9</v>
-      </c>
-      <c r="D322" s="2">
-        <v>0</v>
-      </c>
-      <c r="E322" s="2">
-        <v>5</v>
-      </c>
-      <c r="F322" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G322" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H322" s="2">
-        <v>17</v>
-      </c>
-      <c r="I322" s="2">
-        <v>3</v>
-      </c>
-      <c r="J322" s="2">
-        <v>14</v>
-      </c>
-      <c r="K322" s="2">
-        <v>0.72222222222222221</v>
-      </c>
-      <c r="L322" s="2">
-        <v>0.2078698548207745</v>
-      </c>
-      <c r="M322" s="2">
-        <v>0.61111111111111105</v>
-      </c>
-      <c r="N322" s="2">
-        <v>0.28327886186626577</v>
-      </c>
-      <c r="O322" s="2">
-        <v>1</v>
-      </c>
-      <c r="P322" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q322" s="2">
-        <v>1</v>
-      </c>
-      <c r="R322" s="2">
-        <v>0</v>
-      </c>
-      <c r="S322" s="2">
-        <v>1</v>
-      </c>
-      <c r="T322" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A323" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B323" s="2">
-        <v>9</v>
-      </c>
-      <c r="C323" s="2">
-        <v>9</v>
-      </c>
-      <c r="D323" s="2">
-        <v>0</v>
-      </c>
-      <c r="E323" s="2">
-        <v>5</v>
-      </c>
-      <c r="F323" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G323" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H323" s="2">
-        <v>17</v>
-      </c>
-      <c r="I323" s="2">
-        <v>3</v>
-      </c>
-      <c r="J323" s="2">
-        <v>14</v>
-      </c>
-      <c r="K323" s="2">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="L323" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="M323" s="2">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="N323" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="O323" s="2">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="P323" s="2">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="Q323" s="2">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="R323" s="2">
-        <v>0.23570226039551581</v>
-      </c>
-      <c r="S323" s="2">
-        <v>0.88888888888888895</v>
-      </c>
-      <c r="T323" s="2">
-        <v>0.15713484026367719</v>
-      </c>
-    </row>
-    <row r="324" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A324" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B324" s="2">
-        <v>9</v>
-      </c>
-      <c r="C324" s="2">
-        <v>9</v>
-      </c>
-      <c r="D324" s="2">
-        <v>0</v>
-      </c>
-      <c r="E324" s="2">
-        <v>5</v>
-      </c>
-      <c r="F324" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G324" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H324" s="2">
-        <v>17</v>
-      </c>
-      <c r="I324" s="2">
-        <v>3</v>
-      </c>
-      <c r="J324" s="2">
-        <v>14</v>
-      </c>
-      <c r="K324" s="2">
-        <v>0</v>
-      </c>
-      <c r="L324" s="2">
-        <v>0</v>
-      </c>
-      <c r="M324" s="2">
-        <v>0</v>
-      </c>
-      <c r="N324" s="2">
-        <v>0</v>
-      </c>
-      <c r="O324" s="2">
-        <v>0</v>
-      </c>
-      <c r="P324" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q324" s="2">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="R324" s="2">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="S324" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="T324" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325" spans="1:20" ht="19" x14ac:dyDescent="0.2">
-      <c r="A325" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B325" s="2">
-        <v>9</v>
-      </c>
-      <c r="C325" s="2">
-        <v>9</v>
-      </c>
-      <c r="D325" s="2">
-        <v>0</v>
-      </c>
-      <c r="E325" s="2">
-        <v>5</v>
-      </c>
-      <c r="F325" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G325" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H325" s="2">
-        <v>17</v>
-      </c>
-      <c r="I325" s="2">
-        <v>3</v>
-      </c>
-      <c r="J325" s="2">
-        <v>14</v>
-      </c>
-      <c r="K325" s="2">
-        <v>0</v>
-      </c>
-      <c r="L325" s="2">
-        <v>0</v>
-      </c>
-      <c r="M325" s="2">
-        <v>0</v>
-      </c>
-      <c r="N325" s="2">
-        <v>0</v>
-      </c>
-      <c r="O325" s="2">
-        <v>0</v>
-      </c>
-      <c r="P325" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q325" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="R325" s="2">
-        <v>0.23570226039551581</v>
-      </c>
-      <c r="S325" s="2">
-        <v>0.72222222222222232</v>
-      </c>
-      <c r="T325" s="2">
-        <v>0.2078698548207745</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:T325" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
+  <autoFilter ref="A1:T289" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/RESULTS/hydronewsfr/hydronewsfr_results.xlsx
+++ b/RESULTS/hydronewsfr/hydronewsfr_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/evangeliazve/Documents/Papier EMNLP/Dossier Github - supp material/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEAB7B17-63C1-664D-A694-2662A9F84143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8F723F-89FB-E44A-BAFD-85B749F774FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="31860" yWindow="2680" windowWidth="32240" windowHeight="17000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="ml_metrics_with_ablation" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ml_metrics_with_ablation!$A$1:$S$316</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ml_metrics_with_ablation!$A$1:$S$289</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="33">
   <si>
     <t>toa_max_neg</t>
   </si>
@@ -534,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:S316"/>
+  <dimension ref="A1:S289"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
@@ -17608,1601 +17608,8 @@
         <v>6.9985421222376484E-2</v>
       </c>
     </row>
-    <row r="290" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A290" s="2">
-        <v>9</v>
-      </c>
-      <c r="B290" s="2">
-        <v>9</v>
-      </c>
-      <c r="C290" s="2">
-        <v>0</v>
-      </c>
-      <c r="D290" s="2">
-        <v>5</v>
-      </c>
-      <c r="E290" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G290" s="2">
-        <v>17</v>
-      </c>
-      <c r="H290" s="2">
-        <v>3</v>
-      </c>
-      <c r="I290" s="2">
-        <v>14</v>
-      </c>
-      <c r="J290" s="4">
-        <v>1</v>
-      </c>
-      <c r="K290" s="4">
-        <v>0</v>
-      </c>
-      <c r="L290" s="4">
-        <v>1</v>
-      </c>
-      <c r="M290" s="4">
-        <v>0</v>
-      </c>
-      <c r="N290" s="4">
-        <v>1</v>
-      </c>
-      <c r="O290" s="4">
-        <v>0</v>
-      </c>
-      <c r="P290" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q290" s="4">
-        <v>0</v>
-      </c>
-      <c r="R290" s="4">
-        <v>1</v>
-      </c>
-      <c r="S290" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A291" s="2">
-        <v>9</v>
-      </c>
-      <c r="B291" s="2">
-        <v>9</v>
-      </c>
-      <c r="C291" s="2">
-        <v>0</v>
-      </c>
-      <c r="D291" s="2">
-        <v>5</v>
-      </c>
-      <c r="E291" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F291" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G291" s="2">
-        <v>17</v>
-      </c>
-      <c r="H291" s="2">
-        <v>3</v>
-      </c>
-      <c r="I291" s="2">
-        <v>14</v>
-      </c>
-      <c r="J291" s="4">
-        <v>1</v>
-      </c>
-      <c r="K291" s="4">
-        <v>0</v>
-      </c>
-      <c r="L291" s="4">
-        <v>1</v>
-      </c>
-      <c r="M291" s="4">
-        <v>0</v>
-      </c>
-      <c r="N291" s="4">
-        <v>1</v>
-      </c>
-      <c r="O291" s="4">
-        <v>0</v>
-      </c>
-      <c r="P291" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q291" s="4">
-        <v>0</v>
-      </c>
-      <c r="R291" s="4">
-        <v>1</v>
-      </c>
-      <c r="S291" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A292" s="6">
-        <v>9</v>
-      </c>
-      <c r="B292" s="6">
-        <v>9</v>
-      </c>
-      <c r="C292" s="6">
-        <v>0</v>
-      </c>
-      <c r="D292" s="6">
-        <v>5</v>
-      </c>
-      <c r="E292" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F292" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G292" s="6">
-        <v>17</v>
-      </c>
-      <c r="H292" s="6">
-        <v>3</v>
-      </c>
-      <c r="I292" s="6">
-        <v>14</v>
-      </c>
-      <c r="J292" s="7">
-        <v>0.46666666666666662</v>
-      </c>
-      <c r="K292" s="7">
-        <v>4.7140452079103161E-2</v>
-      </c>
-      <c r="L292" s="7">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="M292" s="7">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="N292" s="7">
-        <v>1</v>
-      </c>
-      <c r="O292" s="7">
-        <v>0</v>
-      </c>
-      <c r="P292" s="7">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="Q292" s="7">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="R292" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="S292" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A293" s="6">
-        <v>9</v>
-      </c>
-      <c r="B293" s="6">
-        <v>9</v>
-      </c>
-      <c r="C293" s="6">
-        <v>0</v>
-      </c>
-      <c r="D293" s="6">
-        <v>5</v>
-      </c>
-      <c r="E293" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F293" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G293" s="6">
-        <v>17</v>
-      </c>
-      <c r="H293" s="6">
-        <v>3</v>
-      </c>
-      <c r="I293" s="6">
-        <v>14</v>
-      </c>
-      <c r="J293" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="K293" s="7">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="L293" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="M293" s="7">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="N293" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="O293" s="7">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="P293" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q293" s="7">
-        <v>0</v>
-      </c>
-      <c r="R293" s="7">
-        <v>1</v>
-      </c>
-      <c r="S293" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A294" s="6">
-        <v>9</v>
-      </c>
-      <c r="B294" s="6">
-        <v>9</v>
-      </c>
-      <c r="C294" s="6">
-        <v>0</v>
-      </c>
-      <c r="D294" s="6">
-        <v>5</v>
-      </c>
-      <c r="E294" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F294" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G294" s="6">
-        <v>17</v>
-      </c>
-      <c r="H294" s="6">
-        <v>3</v>
-      </c>
-      <c r="I294" s="6">
-        <v>14</v>
-      </c>
-      <c r="J294" s="7">
-        <v>0</v>
-      </c>
-      <c r="K294" s="7">
-        <v>0</v>
-      </c>
-      <c r="L294" s="7">
-        <v>0</v>
-      </c>
-      <c r="M294" s="7">
-        <v>0</v>
-      </c>
-      <c r="N294" s="7">
-        <v>0</v>
-      </c>
-      <c r="O294" s="7">
-        <v>0</v>
-      </c>
-      <c r="P294" s="7">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="Q294" s="7">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="R294" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="S294" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A295" s="6">
-        <v>9</v>
-      </c>
-      <c r="B295" s="6">
-        <v>9</v>
-      </c>
-      <c r="C295" s="6">
-        <v>0</v>
-      </c>
-      <c r="D295" s="6">
-        <v>5</v>
-      </c>
-      <c r="E295" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F295" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G295" s="6">
-        <v>17</v>
-      </c>
-      <c r="H295" s="6">
-        <v>3</v>
-      </c>
-      <c r="I295" s="6">
-        <v>14</v>
-      </c>
-      <c r="J295" s="7">
-        <v>0</v>
-      </c>
-      <c r="K295" s="7">
-        <v>0</v>
-      </c>
-      <c r="L295" s="7">
-        <v>0</v>
-      </c>
-      <c r="M295" s="7">
-        <v>0</v>
-      </c>
-      <c r="N295" s="7">
-        <v>0</v>
-      </c>
-      <c r="O295" s="7">
-        <v>0</v>
-      </c>
-      <c r="P295" s="7">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="Q295" s="7">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="R295" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="S295" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A296" s="6">
-        <v>9</v>
-      </c>
-      <c r="B296" s="6">
-        <v>9</v>
-      </c>
-      <c r="C296" s="6">
-        <v>0</v>
-      </c>
-      <c r="D296" s="6">
-        <v>5</v>
-      </c>
-      <c r="E296" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F296" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G296" s="6">
-        <v>17</v>
-      </c>
-      <c r="H296" s="6">
-        <v>3</v>
-      </c>
-      <c r="I296" s="6">
-        <v>14</v>
-      </c>
-      <c r="J296" s="7">
-        <v>0</v>
-      </c>
-      <c r="K296" s="7">
-        <v>0</v>
-      </c>
-      <c r="L296" s="7">
-        <v>0</v>
-      </c>
-      <c r="M296" s="7">
-        <v>0</v>
-      </c>
-      <c r="N296" s="7">
-        <v>0</v>
-      </c>
-      <c r="O296" s="7">
-        <v>0</v>
-      </c>
-      <c r="P296" s="7">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="Q296" s="7">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="R296" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="S296" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A297" s="6">
-        <v>9</v>
-      </c>
-      <c r="B297" s="6">
-        <v>9</v>
-      </c>
-      <c r="C297" s="6">
-        <v>0</v>
-      </c>
-      <c r="D297" s="6">
-        <v>5</v>
-      </c>
-      <c r="E297" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F297" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G297" s="6">
-        <v>17</v>
-      </c>
-      <c r="H297" s="6">
-        <v>3</v>
-      </c>
-      <c r="I297" s="6">
-        <v>14</v>
-      </c>
-      <c r="J297" s="7">
-        <v>0.77777777777777768</v>
-      </c>
-      <c r="K297" s="7">
-        <v>0.15713484026367719</v>
-      </c>
-      <c r="L297" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="M297" s="7">
-        <v>0.23570226039551581</v>
-      </c>
-      <c r="N297" s="7">
-        <v>1</v>
-      </c>
-      <c r="O297" s="7">
-        <v>0</v>
-      </c>
-      <c r="P297" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q297" s="7">
-        <v>0</v>
-      </c>
-      <c r="R297" s="7">
-        <v>1</v>
-      </c>
-      <c r="S297" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A298" s="6">
-        <v>9</v>
-      </c>
-      <c r="B298" s="6">
-        <v>9</v>
-      </c>
-      <c r="C298" s="6">
-        <v>0</v>
-      </c>
-      <c r="D298" s="6">
-        <v>5</v>
-      </c>
-      <c r="E298" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F298" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G298" s="6">
-        <v>17</v>
-      </c>
-      <c r="H298" s="6">
-        <v>3</v>
-      </c>
-      <c r="I298" s="6">
-        <v>14</v>
-      </c>
-      <c r="J298" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="K298" s="7">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="L298" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="M298" s="7">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="N298" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="O298" s="7">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="P298" s="7">
-        <v>0.77777777777777768</v>
-      </c>
-      <c r="Q298" s="7">
-        <v>0.31426968052735449</v>
-      </c>
-      <c r="R298" s="7">
-        <v>0.77777777777777779</v>
-      </c>
-      <c r="S298" s="7">
-        <v>0.31426968052735438</v>
-      </c>
-    </row>
-    <row r="299" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A299" s="6">
-        <v>9</v>
-      </c>
-      <c r="B299" s="6">
-        <v>9</v>
-      </c>
-      <c r="C299" s="6">
-        <v>0</v>
-      </c>
-      <c r="D299" s="6">
-        <v>5</v>
-      </c>
-      <c r="E299" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F299" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G299" s="6">
-        <v>17</v>
-      </c>
-      <c r="H299" s="6">
-        <v>3</v>
-      </c>
-      <c r="I299" s="6">
-        <v>14</v>
-      </c>
-      <c r="J299" s="7">
-        <v>0</v>
-      </c>
-      <c r="K299" s="7">
-        <v>0</v>
-      </c>
-      <c r="L299" s="7">
-        <v>0</v>
-      </c>
-      <c r="M299" s="7">
-        <v>0</v>
-      </c>
-      <c r="N299" s="7">
-        <v>0</v>
-      </c>
-      <c r="O299" s="7">
-        <v>0</v>
-      </c>
-      <c r="P299" s="7">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="Q299" s="7">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="R299" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="S299" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A300" s="6">
-        <v>9</v>
-      </c>
-      <c r="B300" s="6">
-        <v>9</v>
-      </c>
-      <c r="C300" s="6">
-        <v>0</v>
-      </c>
-      <c r="D300" s="6">
-        <v>5</v>
-      </c>
-      <c r="E300" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F300" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G300" s="6">
-        <v>17</v>
-      </c>
-      <c r="H300" s="6">
-        <v>3</v>
-      </c>
-      <c r="I300" s="6">
-        <v>14</v>
-      </c>
-      <c r="J300" s="7">
-        <v>0</v>
-      </c>
-      <c r="K300" s="7">
-        <v>0</v>
-      </c>
-      <c r="L300" s="7">
-        <v>0</v>
-      </c>
-      <c r="M300" s="7">
-        <v>0</v>
-      </c>
-      <c r="N300" s="7">
-        <v>0</v>
-      </c>
-      <c r="O300" s="7">
-        <v>0</v>
-      </c>
-      <c r="P300" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="Q300" s="7">
-        <v>0.23570226039551581</v>
-      </c>
-      <c r="R300" s="7">
-        <v>0.72222222222222232</v>
-      </c>
-      <c r="S300" s="7">
-        <v>0.2078698548207745</v>
-      </c>
-    </row>
-    <row r="301" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A301" s="6">
-        <v>9</v>
-      </c>
-      <c r="B301" s="6">
-        <v>9</v>
-      </c>
-      <c r="C301" s="6">
-        <v>0</v>
-      </c>
-      <c r="D301" s="6">
-        <v>5</v>
-      </c>
-      <c r="E301" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F301" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G301" s="6">
-        <v>17</v>
-      </c>
-      <c r="H301" s="6">
-        <v>3</v>
-      </c>
-      <c r="I301" s="6">
-        <v>14</v>
-      </c>
-      <c r="J301" s="7">
-        <v>0</v>
-      </c>
-      <c r="K301" s="7">
-        <v>0</v>
-      </c>
-      <c r="L301" s="7">
-        <v>0</v>
-      </c>
-      <c r="M301" s="7">
-        <v>0</v>
-      </c>
-      <c r="N301" s="7">
-        <v>0</v>
-      </c>
-      <c r="O301" s="7">
-        <v>0</v>
-      </c>
-      <c r="P301" s="7">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="Q301" s="7">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="R301" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="S301" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A302" s="6">
-        <v>9</v>
-      </c>
-      <c r="B302" s="6">
-        <v>9</v>
-      </c>
-      <c r="C302" s="6">
-        <v>0</v>
-      </c>
-      <c r="D302" s="6">
-        <v>5</v>
-      </c>
-      <c r="E302" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F302" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G302" s="6">
-        <v>17</v>
-      </c>
-      <c r="H302" s="6">
-        <v>3</v>
-      </c>
-      <c r="I302" s="6">
-        <v>14</v>
-      </c>
-      <c r="J302" s="7">
-        <v>1</v>
-      </c>
-      <c r="K302" s="7">
-        <v>0</v>
-      </c>
-      <c r="L302" s="7">
-        <v>1</v>
-      </c>
-      <c r="M302" s="7">
-        <v>0</v>
-      </c>
-      <c r="N302" s="7">
-        <v>1</v>
-      </c>
-      <c r="O302" s="7">
-        <v>0</v>
-      </c>
-      <c r="P302" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q302" s="7">
-        <v>0</v>
-      </c>
-      <c r="R302" s="7">
-        <v>1</v>
-      </c>
-      <c r="S302" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A303" s="6">
-        <v>9</v>
-      </c>
-      <c r="B303" s="6">
-        <v>9</v>
-      </c>
-      <c r="C303" s="6">
-        <v>0</v>
-      </c>
-      <c r="D303" s="6">
-        <v>5</v>
-      </c>
-      <c r="E303" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F303" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G303" s="6">
-        <v>17</v>
-      </c>
-      <c r="H303" s="6">
-        <v>3</v>
-      </c>
-      <c r="I303" s="6">
-        <v>14</v>
-      </c>
-      <c r="J303" s="7">
-        <v>1</v>
-      </c>
-      <c r="K303" s="7">
-        <v>0</v>
-      </c>
-      <c r="L303" s="7">
-        <v>1</v>
-      </c>
-      <c r="M303" s="7">
-        <v>0</v>
-      </c>
-      <c r="N303" s="7">
-        <v>1</v>
-      </c>
-      <c r="O303" s="7">
-        <v>0</v>
-      </c>
-      <c r="P303" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q303" s="7">
-        <v>0</v>
-      </c>
-      <c r="R303" s="7">
-        <v>1</v>
-      </c>
-      <c r="S303" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A304" s="6">
-        <v>9</v>
-      </c>
-      <c r="B304" s="6">
-        <v>9</v>
-      </c>
-      <c r="C304" s="6">
-        <v>0</v>
-      </c>
-      <c r="D304" s="6">
-        <v>5</v>
-      </c>
-      <c r="E304" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F304" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G304" s="6">
-        <v>17</v>
-      </c>
-      <c r="H304" s="6">
-        <v>3</v>
-      </c>
-      <c r="I304" s="6">
-        <v>14</v>
-      </c>
-      <c r="J304" s="7">
-        <v>0</v>
-      </c>
-      <c r="K304" s="7">
-        <v>0</v>
-      </c>
-      <c r="L304" s="7">
-        <v>0</v>
-      </c>
-      <c r="M304" s="7">
-        <v>0</v>
-      </c>
-      <c r="N304" s="7">
-        <v>0</v>
-      </c>
-      <c r="O304" s="7">
-        <v>0</v>
-      </c>
-      <c r="P304" s="7">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="Q304" s="7">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="R304" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="S304" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A305" s="6">
-        <v>9</v>
-      </c>
-      <c r="B305" s="6">
-        <v>9</v>
-      </c>
-      <c r="C305" s="6">
-        <v>0</v>
-      </c>
-      <c r="D305" s="6">
-        <v>5</v>
-      </c>
-      <c r="E305" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F305" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G305" s="6">
-        <v>17</v>
-      </c>
-      <c r="H305" s="6">
-        <v>3</v>
-      </c>
-      <c r="I305" s="6">
-        <v>14</v>
-      </c>
-      <c r="J305" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="K305" s="7">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="L305" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="M305" s="7">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="N305" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="O305" s="7">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="P305" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q305" s="7">
-        <v>0</v>
-      </c>
-      <c r="R305" s="7">
-        <v>1</v>
-      </c>
-      <c r="S305" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A306" s="6">
-        <v>9</v>
-      </c>
-      <c r="B306" s="6">
-        <v>9</v>
-      </c>
-      <c r="C306" s="6">
-        <v>0</v>
-      </c>
-      <c r="D306" s="6">
-        <v>5</v>
-      </c>
-      <c r="E306" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F306" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G306" s="6">
-        <v>17</v>
-      </c>
-      <c r="H306" s="6">
-        <v>3</v>
-      </c>
-      <c r="I306" s="6">
-        <v>14</v>
-      </c>
-      <c r="J306" s="7">
-        <v>0</v>
-      </c>
-      <c r="K306" s="7">
-        <v>0</v>
-      </c>
-      <c r="L306" s="7">
-        <v>0</v>
-      </c>
-      <c r="M306" s="7">
-        <v>0</v>
-      </c>
-      <c r="N306" s="7">
-        <v>0</v>
-      </c>
-      <c r="O306" s="7">
-        <v>0</v>
-      </c>
-      <c r="P306" s="7">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="Q306" s="7">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="R306" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="S306" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A307" s="6">
-        <v>9</v>
-      </c>
-      <c r="B307" s="6">
-        <v>9</v>
-      </c>
-      <c r="C307" s="6">
-        <v>0</v>
-      </c>
-      <c r="D307" s="6">
-        <v>5</v>
-      </c>
-      <c r="E307" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F307" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G307" s="6">
-        <v>17</v>
-      </c>
-      <c r="H307" s="6">
-        <v>3</v>
-      </c>
-      <c r="I307" s="6">
-        <v>14</v>
-      </c>
-      <c r="J307" s="7">
-        <v>1</v>
-      </c>
-      <c r="K307" s="7">
-        <v>0</v>
-      </c>
-      <c r="L307" s="7">
-        <v>1</v>
-      </c>
-      <c r="M307" s="7">
-        <v>0</v>
-      </c>
-      <c r="N307" s="7">
-        <v>1</v>
-      </c>
-      <c r="O307" s="7">
-        <v>0</v>
-      </c>
-      <c r="P307" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q307" s="7">
-        <v>0</v>
-      </c>
-      <c r="R307" s="7">
-        <v>1</v>
-      </c>
-      <c r="S307" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A308" s="6">
-        <v>9</v>
-      </c>
-      <c r="B308" s="6">
-        <v>9</v>
-      </c>
-      <c r="C308" s="6">
-        <v>0</v>
-      </c>
-      <c r="D308" s="6">
-        <v>5</v>
-      </c>
-      <c r="E308" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F308" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G308" s="6">
-        <v>17</v>
-      </c>
-      <c r="H308" s="6">
-        <v>3</v>
-      </c>
-      <c r="I308" s="6">
-        <v>14</v>
-      </c>
-      <c r="J308" s="7">
-        <v>0.88888888888888884</v>
-      </c>
-      <c r="K308" s="7">
-        <v>0.15713484026367719</v>
-      </c>
-      <c r="L308" s="7">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="M308" s="7">
-        <v>0.23570226039551581</v>
-      </c>
-      <c r="N308" s="7">
-        <v>1</v>
-      </c>
-      <c r="O308" s="7">
-        <v>0</v>
-      </c>
-      <c r="P308" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q308" s="7">
-        <v>0</v>
-      </c>
-      <c r="R308" s="7">
-        <v>1</v>
-      </c>
-      <c r="S308" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A309" s="6">
-        <v>9</v>
-      </c>
-      <c r="B309" s="6">
-        <v>9</v>
-      </c>
-      <c r="C309" s="6">
-        <v>0</v>
-      </c>
-      <c r="D309" s="6">
-        <v>5</v>
-      </c>
-      <c r="E309" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F309" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G309" s="6">
-        <v>17</v>
-      </c>
-      <c r="H309" s="6">
-        <v>3</v>
-      </c>
-      <c r="I309" s="6">
-        <v>14</v>
-      </c>
-      <c r="J309" s="7">
-        <v>0</v>
-      </c>
-      <c r="K309" s="7">
-        <v>0</v>
-      </c>
-      <c r="L309" s="7">
-        <v>0</v>
-      </c>
-      <c r="M309" s="7">
-        <v>0</v>
-      </c>
-      <c r="N309" s="7">
-        <v>0</v>
-      </c>
-      <c r="O309" s="7">
-        <v>0</v>
-      </c>
-      <c r="P309" s="7">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="Q309" s="7">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="R309" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="S309" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A310" s="6">
-        <v>9</v>
-      </c>
-      <c r="B310" s="6">
-        <v>9</v>
-      </c>
-      <c r="C310" s="6">
-        <v>0</v>
-      </c>
-      <c r="D310" s="6">
-        <v>5</v>
-      </c>
-      <c r="E310" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F310" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G310" s="6">
-        <v>17</v>
-      </c>
-      <c r="H310" s="6">
-        <v>3</v>
-      </c>
-      <c r="I310" s="6">
-        <v>14</v>
-      </c>
-      <c r="J310" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="K310" s="7">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="L310" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="M310" s="7">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="N310" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="O310" s="7">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="P310" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q310" s="7">
-        <v>0</v>
-      </c>
-      <c r="R310" s="7">
-        <v>1</v>
-      </c>
-      <c r="S310" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A311" s="6">
-        <v>9</v>
-      </c>
-      <c r="B311" s="6">
-        <v>9</v>
-      </c>
-      <c r="C311" s="6">
-        <v>0</v>
-      </c>
-      <c r="D311" s="6">
-        <v>5</v>
-      </c>
-      <c r="E311" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F311" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G311" s="6">
-        <v>17</v>
-      </c>
-      <c r="H311" s="6">
-        <v>3</v>
-      </c>
-      <c r="I311" s="6">
-        <v>14</v>
-      </c>
-      <c r="J311" s="7">
-        <v>0</v>
-      </c>
-      <c r="K311" s="7">
-        <v>0</v>
-      </c>
-      <c r="L311" s="7">
-        <v>0</v>
-      </c>
-      <c r="M311" s="7">
-        <v>0</v>
-      </c>
-      <c r="N311" s="7">
-        <v>0</v>
-      </c>
-      <c r="O311" s="7">
-        <v>0</v>
-      </c>
-      <c r="P311" s="7">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="Q311" s="7">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="R311" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="S311" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A312" s="6">
-        <v>9</v>
-      </c>
-      <c r="B312" s="6">
-        <v>9</v>
-      </c>
-      <c r="C312" s="6">
-        <v>0</v>
-      </c>
-      <c r="D312" s="6">
-        <v>5</v>
-      </c>
-      <c r="E312" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F312" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G312" s="6">
-        <v>17</v>
-      </c>
-      <c r="H312" s="6">
-        <v>3</v>
-      </c>
-      <c r="I312" s="6">
-        <v>14</v>
-      </c>
-      <c r="J312" s="7">
-        <v>1</v>
-      </c>
-      <c r="K312" s="7">
-        <v>0</v>
-      </c>
-      <c r="L312" s="7">
-        <v>1</v>
-      </c>
-      <c r="M312" s="7">
-        <v>0</v>
-      </c>
-      <c r="N312" s="7">
-        <v>1</v>
-      </c>
-      <c r="O312" s="7">
-        <v>0</v>
-      </c>
-      <c r="P312" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q312" s="7">
-        <v>0</v>
-      </c>
-      <c r="R312" s="7">
-        <v>1</v>
-      </c>
-      <c r="S312" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A313" s="6">
-        <v>9</v>
-      </c>
-      <c r="B313" s="6">
-        <v>9</v>
-      </c>
-      <c r="C313" s="6">
-        <v>0</v>
-      </c>
-      <c r="D313" s="6">
-        <v>5</v>
-      </c>
-      <c r="E313" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F313" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G313" s="6">
-        <v>17</v>
-      </c>
-      <c r="H313" s="6">
-        <v>3</v>
-      </c>
-      <c r="I313" s="6">
-        <v>14</v>
-      </c>
-      <c r="J313" s="7">
-        <v>1</v>
-      </c>
-      <c r="K313" s="7">
-        <v>0</v>
-      </c>
-      <c r="L313" s="7">
-        <v>1</v>
-      </c>
-      <c r="M313" s="7">
-        <v>0</v>
-      </c>
-      <c r="N313" s="7">
-        <v>1</v>
-      </c>
-      <c r="O313" s="7">
-        <v>0</v>
-      </c>
-      <c r="P313" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q313" s="7">
-        <v>0</v>
-      </c>
-      <c r="R313" s="7">
-        <v>1</v>
-      </c>
-      <c r="S313" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A314" s="6">
-        <v>9</v>
-      </c>
-      <c r="B314" s="6">
-        <v>9</v>
-      </c>
-      <c r="C314" s="6">
-        <v>0</v>
-      </c>
-      <c r="D314" s="6">
-        <v>5</v>
-      </c>
-      <c r="E314" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F314" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G314" s="6">
-        <v>17</v>
-      </c>
-      <c r="H314" s="6">
-        <v>3</v>
-      </c>
-      <c r="I314" s="6">
-        <v>14</v>
-      </c>
-      <c r="J314" s="7">
-        <v>0</v>
-      </c>
-      <c r="K314" s="7">
-        <v>0</v>
-      </c>
-      <c r="L314" s="7">
-        <v>0</v>
-      </c>
-      <c r="M314" s="7">
-        <v>0</v>
-      </c>
-      <c r="N314" s="7">
-        <v>0</v>
-      </c>
-      <c r="O314" s="7">
-        <v>0</v>
-      </c>
-      <c r="P314" s="7">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="Q314" s="7">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="R314" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="S314" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A315" s="6">
-        <v>9</v>
-      </c>
-      <c r="B315" s="6">
-        <v>9</v>
-      </c>
-      <c r="C315" s="6">
-        <v>0</v>
-      </c>
-      <c r="D315" s="6">
-        <v>5</v>
-      </c>
-      <c r="E315" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F315" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G315" s="6">
-        <v>17</v>
-      </c>
-      <c r="H315" s="6">
-        <v>3</v>
-      </c>
-      <c r="I315" s="6">
-        <v>14</v>
-      </c>
-      <c r="J315" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="K315" s="7">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="L315" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="M315" s="7">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="N315" s="7">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="O315" s="7">
-        <v>0.47140452079103168</v>
-      </c>
-      <c r="P315" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q315" s="7">
-        <v>0</v>
-      </c>
-      <c r="R315" s="7">
-        <v>1</v>
-      </c>
-      <c r="S315" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316" spans="1:19" ht="19" x14ac:dyDescent="0.2">
-      <c r="A316" s="6">
-        <v>9</v>
-      </c>
-      <c r="B316" s="6">
-        <v>9</v>
-      </c>
-      <c r="C316" s="6">
-        <v>0</v>
-      </c>
-      <c r="D316" s="6">
-        <v>5</v>
-      </c>
-      <c r="E316" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F316" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G316" s="6">
-        <v>17</v>
-      </c>
-      <c r="H316" s="6">
-        <v>3</v>
-      </c>
-      <c r="I316" s="6">
-        <v>14</v>
-      </c>
-      <c r="J316" s="7">
-        <v>0</v>
-      </c>
-      <c r="K316" s="7">
-        <v>0</v>
-      </c>
-      <c r="L316" s="7">
-        <v>0</v>
-      </c>
-      <c r="M316" s="7">
-        <v>0</v>
-      </c>
-      <c r="N316" s="7">
-        <v>0</v>
-      </c>
-      <c r="O316" s="7">
-        <v>0</v>
-      </c>
-      <c r="P316" s="7">
-        <v>0.30555555555555552</v>
-      </c>
-      <c r="Q316" s="7">
-        <v>3.9283710065919297E-2</v>
-      </c>
-      <c r="R316" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="S316" s="7">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:S316" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
+  <autoFilter ref="A1:S289" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S273">
     <sortCondition ref="A2:A273"/>
     <sortCondition ref="E2:E273"/>
